--- a/uploads/test_delete.xlsx
+++ b/uploads/test_delete.xlsx
@@ -464,7 +464,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>67</v>
+        <v>280</v>
       </c>
       <c r="E2" t="n">
         <v>2</v>

--- a/uploads/test_delete.xlsx
+++ b/uploads/test_delete.xlsx
@@ -464,7 +464,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>280</v>
+        <v>350</v>
       </c>
       <c r="E2" t="n">
         <v>2</v>

--- a/uploads/test_delete.xlsx
+++ b/uploads/test_delete.xlsx
@@ -464,7 +464,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>350</v>
+        <v>561</v>
       </c>
       <c r="E2" t="n">
         <v>2</v>

--- a/uploads/test_delete.xlsx
+++ b/uploads/test_delete.xlsx
@@ -464,7 +464,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>561</v>
+        <v>749</v>
       </c>
       <c r="E2" t="n">
         <v>2</v>
